--- a/experiment/questions.xlsx
+++ b/experiment/questions.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="369">
   <si>
     <t>Story</t>
   </si>
@@ -211,6 +211,9 @@
     <t>Omdat hij een erfgenaam wilde hebben.</t>
   </si>
   <si>
+    <t>Om twee koninkrijken samen te brengen</t>
+  </si>
+  <si>
     <t>Hoe reageerde het volk op het nieuws van Halichems aanstaande huwelijk?</t>
   </si>
   <si>
@@ -223,6 +226,9 @@
     <t>Ze protesteerden en wilden de bruiloft annuleren.</t>
   </si>
   <si>
+    <t>Ze vonden het nieuws niet zo interessant</t>
+  </si>
+  <si>
     <t>Wat was het grootste probleem dat Halichem met zijn nieuwe koningin had?</t>
   </si>
   <si>
@@ -238,10 +244,10 @@
     <t>Ze was te klein voor hem.</t>
   </si>
   <si>
-    <t>Hoe zijn de bergen in Limburg ontstaan, volgens dit verhaal?</t>
-  </si>
-  <si>
-    <t>Alle reuzen begonnen weg te rennen omdat Halichem heel hard begon te huilen/schreeuwen/bulderen</t>
+    <t>Hoe zijn de heuvels in Limburg ontstaan, volgens dit verhaal?</t>
+  </si>
+  <si>
+    <t>De reuzen hebben de dalen in de grond gestampt toen ze wegrenden voor koning Halichem</t>
   </si>
   <si>
     <t>Daaronder liggen de botten van de gestorven reuzen</t>
@@ -250,6 +256,12 @@
     <t>De reuzen hebben de heuvels daar neergegooid</t>
   </si>
   <si>
+    <t>Oude rivieren hebben de dalen in het landschap gevormd</t>
+  </si>
+  <si>
+    <t>Laura: I categorised this one as local, but now I actually think it might be a bridging question?</t>
+  </si>
+  <si>
     <t>Wat is voor de reuzen de belangrijkste eigenschap van een toekomstige vrouw?</t>
   </si>
   <si>
@@ -262,6 +274,9 @@
     <t>Ze moet veel praten</t>
   </si>
   <si>
+    <t>Ze moet goed kunnen koken</t>
+  </si>
+  <si>
     <t>Hoe lang leven de reuzen ongeveer?</t>
   </si>
   <si>
@@ -277,6 +292,21 @@
     <t>Ze kunnen niet sterven door oude leeftijd, alleen ongelukken</t>
   </si>
   <si>
+    <t>Waarom wilde het volk dat Halichem ging trouwen?</t>
+  </si>
+  <si>
+    <t>Er moest een prins geboren worden voordat Halichem zou sterven</t>
+  </si>
+  <si>
+    <t>Dan hadden ze een reden om feest te vieren</t>
+  </si>
+  <si>
+    <t>In de hoop dat Halichem minder streng zou regeren als hij een vrouw zou hebben</t>
+  </si>
+  <si>
+    <t>Laura: We can merge this question with question 3</t>
+  </si>
+  <si>
     <t>Wat vonden de reuzen over Halichem als koning?</t>
   </si>
   <si>
@@ -373,7 +403,13 @@
     <t>Wat leidde tot het besluit van Groot-Brittannië om militaire actie te ondernemen?</t>
   </si>
   <si>
-    <t>Omdat de Chinezen de opiumhandel niet meer wilden toestaan en de voorraad innamen</t>
+    <t>De Chinezen wilden de opiumhandel niet meer toestaan en namen de voorraad in</t>
+  </si>
+  <si>
+    <t>De Chinezen waren begonnen met aanvallen</t>
+  </si>
+  <si>
+    <t>De chinezen wilden helemaal niet meer handelen met de Britten</t>
   </si>
   <si>
     <t>Aspasia</t>
@@ -406,6 +442,9 @@
     <t>Ze was een beroemde krijgsvrouw</t>
   </si>
   <si>
+    <t>Ze was een beruchte dief</t>
+  </si>
+  <si>
     <t>Waarom was Aspasia vrijgesteld van de wettelijke bepalingen die getrouwde vrouwen aan hun huis bonden?</t>
   </si>
   <si>
@@ -673,6 +712,9 @@
     <t>Omdat hij haar leuk vond</t>
   </si>
   <si>
+    <t>Omdat hij van plan was op het schoolbal te vernederen</t>
+  </si>
+  <si>
     <t>Waarom wordt Carrie boos en slaat ze door tijdens het schoolbal?</t>
   </si>
   <si>
@@ -683,6 +725,9 @@
   </si>
   <si>
     <t>Ze was voor het bal al van plan om wraak te nemen op haar klasgenoten</t>
+  </si>
+  <si>
+    <t>Omdat ze gedrogeerd was</t>
   </si>
   <si>
     <t>Comment Laura: deze vraag moet nog beter verwoord worden.</t>
@@ -1378,7 +1423,7 @@
     <col customWidth="1" min="7" max="7" width="16.38"/>
     <col customWidth="1" min="8" max="8" width="16.88"/>
     <col customWidth="1" min="9" max="9" width="11.0"/>
-    <col customWidth="1" min="10" max="10" width="28.13"/>
+    <col customWidth="1" min="10" max="10" width="34.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1965,7 +2010,9 @@
       <c r="G13" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H13" s="5"/>
+      <c r="H13" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="I13" s="3" t="s">
         <v>22</v>
       </c>
@@ -2000,18 +2047,20 @@
         <v>4.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H14" s="5"/>
+        <v>70</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="I14" s="3" t="s">
         <v>16</v>
       </c>
@@ -2046,19 +2095,19 @@
         <v>5.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>16</v>
@@ -2094,22 +2143,26 @@
         <v>6.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="I16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J16" s="5"/>
+      <c r="J16" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
@@ -2140,18 +2193,20 @@
         <v>7.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H17" s="5"/>
+        <v>86</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="I17" s="3" t="s">
         <v>16</v>
       </c>
@@ -2186,19 +2241,19 @@
         <v>8.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>16</v>
@@ -2233,15 +2288,23 @@
       <c r="C19" s="3">
         <v>9.0</v>
       </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
+      <c r="D19" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="H19" s="3"/>
-      <c r="I19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="5"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
@@ -2272,19 +2335,19 @@
         <v>10.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>50</v>
@@ -2349,31 +2412,21 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="B22" s="3">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="C22" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>98</v>
-      </c>
+        <v>12.0</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
       <c r="I22" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
@@ -2397,31 +2450,31 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B23" s="3">
         <v>3.0</v>
       </c>
       <c r="C23" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
@@ -2445,31 +2498,31 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B24" s="3">
         <v>3.0</v>
       </c>
       <c r="C24" s="3">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
@@ -2493,28 +2546,28 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B25" s="3">
         <v>3.0</v>
       </c>
       <c r="C25" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>16</v>
@@ -2541,28 +2594,28 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B26" s="3">
         <v>3.0</v>
       </c>
       <c r="C26" s="3">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>16</v>
@@ -2589,23 +2642,29 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B27" s="3">
         <v>3.0</v>
       </c>
       <c r="C27" s="3">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
+        <v>125</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="I27" s="3" t="s">
         <v>16</v>
       </c>
@@ -2631,21 +2690,29 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B28" s="3">
         <v>3.0</v>
       </c>
       <c r="C28" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
+        <v>6.0</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>132</v>
+      </c>
       <c r="H28" s="5"/>
       <c r="I28" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
@@ -2669,13 +2736,13 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B29" s="3">
         <v>3.0</v>
       </c>
       <c r="C29" s="3">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -2683,7 +2750,7 @@
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
       <c r="I29" s="3" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
@@ -2707,13 +2774,13 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B30" s="3">
         <v>3.0</v>
       </c>
       <c r="C30" s="3">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -2745,31 +2812,21 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="B31" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C31" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>126</v>
-      </c>
+        <v>9.0</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
       <c r="I31" s="3" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
@@ -2793,27 +2850,29 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="B32" s="3">
         <v>4.0</v>
       </c>
       <c r="C32" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="H32" s="5"/>
+        <v>137</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>138</v>
+      </c>
       <c r="I32" s="3" t="s">
         <v>16</v>
       </c>
@@ -2839,28 +2898,28 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="B33" s="3">
         <v>4.0</v>
       </c>
       <c r="C33" s="3">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>135</v>
+        <v>142</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>143</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>16</v>
@@ -2887,28 +2946,28 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="B34" s="3">
         <v>4.0</v>
       </c>
       <c r="C34" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>136</v>
+        <v>3.0</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>144</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>16</v>
@@ -2935,31 +2994,31 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="B35" s="3">
         <v>4.0</v>
       </c>
       <c r="C35" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="D35" s="6" t="s">
+        <v>4.0</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F35" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>140</v>
-      </c>
       <c r="G35" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
@@ -2983,31 +3042,31 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="B36" s="3">
         <v>4.0</v>
       </c>
       <c r="C36" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>146</v>
+        <v>5.0</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>154</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
@@ -3031,28 +3090,28 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="B37" s="3">
         <v>4.0</v>
       </c>
       <c r="C37" s="3">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>16</v>
@@ -3079,21 +3138,31 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="B38" s="3">
         <v>4.0</v>
       </c>
       <c r="C38" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="5"/>
+        <v>7.0</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>165</v>
+      </c>
       <c r="I38" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
@@ -3117,13 +3186,13 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="B39" s="3">
         <v>4.0</v>
       </c>
       <c r="C39" s="3">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -3131,7 +3200,7 @@
       <c r="G39" s="3"/>
       <c r="H39" s="5"/>
       <c r="I39" s="3" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
@@ -3155,13 +3224,13 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="B40" s="3">
         <v>4.0</v>
       </c>
       <c r="C40" s="3">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -3193,31 +3262,21 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="B41" s="3">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="C41" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>158</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="5"/>
       <c r="I41" s="3" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
@@ -3241,28 +3300,28 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B42" s="3">
         <v>5.0</v>
       </c>
       <c r="C42" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>159</v>
+        <v>1.0</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>167</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>171</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>16</v>
@@ -3289,28 +3348,28 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B43" s="3">
         <v>5.0</v>
       </c>
       <c r="C43" s="3">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>167</v>
+        <v>174</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>175</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>16</v>
@@ -3337,28 +3396,28 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B44" s="3">
         <v>5.0</v>
       </c>
       <c r="C44" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>169</v>
+        <v>3.0</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>177</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>173</v>
+        <v>178</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>16</v>
@@ -3385,31 +3444,31 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B45" s="3">
         <v>5.0</v>
       </c>
       <c r="C45" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>174</v>
+        <v>4.0</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>176</v>
+        <v>183</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>178</v>
+        <v>185</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>186</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
@@ -3433,31 +3492,31 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B46" s="3">
         <v>5.0</v>
       </c>
       <c r="C46" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>179</v>
+        <v>5.0</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>187</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
@@ -3481,21 +3540,31 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B47" s="3">
         <v>5.0</v>
       </c>
       <c r="C47" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="D47" s="3"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>196</v>
+      </c>
       <c r="I47" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
@@ -3519,13 +3588,13 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B48" s="3">
         <v>5.0</v>
       </c>
       <c r="C48" s="3">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="7"/>
@@ -3533,7 +3602,7 @@
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
@@ -3557,13 +3626,13 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B49" s="3">
         <v>5.0</v>
       </c>
       <c r="C49" s="3">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="7"/>
@@ -3595,31 +3664,21 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="B50" s="3">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="C50" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="G50" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>189</v>
-      </c>
+        <v>9.0</v>
+      </c>
+      <c r="D50" s="3"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
       <c r="I50" s="3" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
@@ -3643,31 +3702,31 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B51" s="3">
         <v>6.0</v>
       </c>
       <c r="C51" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>191</v>
+        <v>198</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>199</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="H51" s="8" t="s">
-        <v>194</v>
+        <v>201</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
@@ -3691,31 +3750,31 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B52" s="3">
         <v>6.0</v>
       </c>
       <c r="C52" s="3">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>197</v>
+        <v>204</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>205</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J52" s="5"/>
       <c r="K52" s="5"/>
@@ -3739,28 +3798,28 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B53" s="3">
         <v>6.0</v>
       </c>
       <c r="C53" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>202</v>
+        <v>3.0</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>210</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>204</v>
+        <v>211</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>212</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>16</v>
@@ -3787,28 +3846,28 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B54" s="3">
         <v>6.0</v>
       </c>
       <c r="C54" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>206</v>
+        <v>4.0</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="H54" s="8" t="s">
-        <v>209</v>
+        <v>216</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>217</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>16</v>
@@ -3835,35 +3894,33 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B55" s="3">
         <v>6.0</v>
       </c>
       <c r="C55" s="3">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>222</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>215</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="J55" s="5"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
@@ -3885,31 +3942,35 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B56" s="3">
         <v>6.0</v>
       </c>
       <c r="C56" s="3">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="H56" s="5"/>
+        <v>225</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>227</v>
+      </c>
       <c r="I56" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J56" s="5"/>
+        <v>22</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>228</v>
+      </c>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
@@ -3931,33 +3992,33 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B57" s="3">
         <v>6.0</v>
       </c>
       <c r="C57" s="3">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="H57" s="5"/>
+        <v>232</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>233</v>
+      </c>
       <c r="I57" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>224</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="J57" s="5"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
@@ -3979,25 +4040,35 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B58" s="3">
         <v>6.0</v>
       </c>
       <c r="C58" s="3">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="5"/>
+        <v>234</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>238</v>
+      </c>
       <c r="I58" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J58" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>239</v>
+      </c>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
@@ -4019,26 +4090,20 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B59" s="3">
         <v>6.0</v>
       </c>
       <c r="C59" s="3">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>229</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
       <c r="H59" s="5"/>
       <c r="I59" s="3" t="s">
         <v>50</v>
@@ -4065,33 +4130,31 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="B60" s="3">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="C60" s="3">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="H60" s="8" t="s">
-        <v>235</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="H60" s="5"/>
       <c r="I60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J60" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J60" s="3"/>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
@@ -4113,28 +4176,28 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="B61" s="3">
         <v>7.0</v>
       </c>
       <c r="C61" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>237</v>
+        <v>246</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>247</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>240</v>
+        <v>249</v>
+      </c>
+      <c r="H61" s="8" t="s">
+        <v>250</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>16</v>
@@ -4161,28 +4224,28 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="B62" s="3">
         <v>7.0</v>
       </c>
       <c r="C62" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>242</v>
+        <v>2.0</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>252</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="H62" s="8" t="s">
-        <v>245</v>
+        <v>254</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>255</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>16</v>
@@ -4209,29 +4272,31 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="B63" s="3">
         <v>7.0</v>
       </c>
       <c r="C63" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>247</v>
+        <v>3.0</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>257</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="H63" s="5"/>
+        <v>259</v>
+      </c>
+      <c r="H63" s="8" t="s">
+        <v>260</v>
+      </c>
       <c r="I63" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
@@ -4255,31 +4320,29 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="B64" s="3">
         <v>7.0</v>
       </c>
       <c r="C64" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>251</v>
+        <v>4.0</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>262</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H64" s="8" t="s">
-        <v>254</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="H64" s="5"/>
       <c r="I64" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
@@ -4303,23 +4366,29 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="B65" s="3">
         <v>7.0</v>
       </c>
       <c r="C65" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>255</v>
+        <v>5.0</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>265</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
+        <v>266</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="H65" s="8" t="s">
+        <v>269</v>
+      </c>
       <c r="I65" s="3" t="s">
         <v>16</v>
       </c>
@@ -4343,31 +4412,25 @@
       <c r="AA65" s="5"/>
       <c r="AB65" s="5"/>
     </row>
-    <row r="66" ht="64.5" customHeight="1">
+    <row r="66">
       <c r="A66" s="3" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="B66" s="3">
         <v>7.0</v>
       </c>
       <c r="C66" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>257</v>
+        <v>6.0</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>270</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="H66" s="8" t="s">
-        <v>261</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
       <c r="I66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4391,29 +4454,31 @@
       <c r="AA66" s="5"/>
       <c r="AB66" s="5"/>
     </row>
-    <row r="67">
+    <row r="67" ht="64.5" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="B67" s="3">
         <v>7.0</v>
       </c>
       <c r="C67" s="3">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="G67" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="H67" s="5"/>
+        <v>274</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>276</v>
+      </c>
       <c r="I67" s="3" t="s">
         <v>16</v>
       </c>
@@ -4439,21 +4504,29 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="B68" s="3">
         <v>7.0</v>
       </c>
       <c r="C68" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="D68" s="3"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
+        <v>8.0</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>280</v>
+      </c>
       <c r="H68" s="5"/>
       <c r="I68" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
@@ -4477,13 +4550,13 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="B69" s="3">
         <v>7.0</v>
       </c>
       <c r="C69" s="3">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="8"/>
@@ -4491,7 +4564,7 @@
       <c r="G69" s="8"/>
       <c r="H69" s="5"/>
       <c r="I69" s="3" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="J69" s="5"/>
       <c r="K69" s="5"/>
@@ -4515,13 +4588,13 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="B70" s="3">
         <v>7.0</v>
       </c>
       <c r="C70" s="3">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="D70" s="3"/>
       <c r="E70" s="8"/>
@@ -4553,29 +4626,21 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="B71" s="3">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="C71" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G71" s="8" t="s">
-        <v>270</v>
-      </c>
+        <v>11.0</v>
+      </c>
+      <c r="D71" s="3"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="8"/>
+      <c r="G71" s="8"/>
       <c r="H71" s="5"/>
       <c r="I71" s="3" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="J71" s="5"/>
       <c r="K71" s="5"/>
@@ -4599,33 +4664,31 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="B72" s="3">
         <v>8.0</v>
       </c>
       <c r="C72" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>271</v>
+        <v>1.0</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>282</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="H72" s="5"/>
       <c r="I72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>275</v>
-      </c>
+      <c r="J72" s="5"/>
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
       <c r="M72" s="5"/>
@@ -4647,31 +4710,33 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="B73" s="3">
         <v>8.0</v>
       </c>
       <c r="C73" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>276</v>
+        <v>2.0</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>286</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>279</v>
+        <v>287</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>289</v>
       </c>
       <c r="H73" s="5"/>
       <c r="I73" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J73" s="5"/>
+      <c r="J73" s="3" t="s">
+        <v>290</v>
+      </c>
       <c r="K73" s="5"/>
       <c r="L73" s="5"/>
       <c r="M73" s="5"/>
@@ -4693,33 +4758,31 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="B74" s="3">
         <v>8.0</v>
       </c>
       <c r="C74" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="G74" s="8" t="s">
-        <v>283</v>
+        <v>293</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>294</v>
       </c>
       <c r="H74" s="5"/>
       <c r="I74" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J74" s="3" t="s">
-        <v>284</v>
-      </c>
+      <c r="J74" s="5"/>
       <c r="K74" s="5"/>
       <c r="L74" s="5"/>
       <c r="M74" s="5"/>
@@ -4741,27 +4804,33 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="B75" s="3">
         <v>8.0</v>
       </c>
       <c r="C75" s="3">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
+        <v>296</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>298</v>
+      </c>
       <c r="H75" s="5"/>
       <c r="I75" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J75" s="5"/>
+      <c r="J75" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="K75" s="5"/>
       <c r="L75" s="5"/>
       <c r="M75" s="5"/>
@@ -4783,19 +4852,19 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="B76" s="3">
         <v>8.0</v>
       </c>
       <c r="C76" s="3">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
@@ -4825,19 +4894,19 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="B77" s="3">
         <v>8.0</v>
       </c>
       <c r="C77" s="3">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
@@ -4867,21 +4936,25 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="B78" s="3">
         <v>8.0</v>
       </c>
       <c r="C78" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
+        <v>7.0</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>305</v>
+      </c>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
       <c r="I78" s="3" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="J78" s="5"/>
       <c r="K78" s="5"/>
@@ -4905,13 +4978,13 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="B79" s="3">
         <v>8.0</v>
       </c>
       <c r="C79" s="3">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="D79" s="8"/>
       <c r="E79" s="8"/>
@@ -4943,31 +5016,21 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="B80" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="C80" s="3">
         <v>9.0</v>
       </c>
-      <c r="C80" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="H80" s="8" t="s">
-        <v>296</v>
-      </c>
+      <c r="D80" s="8"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
       <c r="I80" s="3" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="J80" s="5"/>
       <c r="K80" s="5"/>
@@ -4991,31 +5054,31 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B81" s="3">
         <v>9.0</v>
       </c>
       <c r="C81" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>298</v>
+        <v>307</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>308</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J81" s="5"/>
       <c r="K81" s="5"/>
@@ -5039,31 +5102,31 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B82" s="3">
         <v>9.0</v>
       </c>
       <c r="C82" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="D82" s="8" t="s">
-        <v>302</v>
+        <v>2.0</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>312</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J82" s="5"/>
       <c r="K82" s="5"/>
@@ -5087,27 +5150,29 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B83" s="3">
         <v>9.0</v>
       </c>
       <c r="C83" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>307</v>
+        <v>3.0</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>317</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="H83" s="5"/>
+        <v>320</v>
+      </c>
+      <c r="H83" s="8" t="s">
+        <v>321</v>
+      </c>
       <c r="I83" s="3" t="s">
         <v>16</v>
       </c>
@@ -5133,29 +5198,27 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B84" s="3">
         <v>9.0</v>
       </c>
       <c r="C84" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="D84" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="G84" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>315</v>
-      </c>
+        <v>4.0</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="H84" s="5"/>
       <c r="I84" s="3" t="s">
         <v>16</v>
       </c>
@@ -5181,28 +5244,28 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B85" s="3">
         <v>9.0</v>
       </c>
       <c r="C85" s="3">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="F85" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="H85" s="8" t="s">
-        <v>320</v>
+        <v>327</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>330</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>16</v>
@@ -5229,28 +5292,28 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B86" s="3">
         <v>9.0</v>
       </c>
       <c r="C86" s="3">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="E86" s="8" t="s">
-        <v>322</v>
+        <v>331</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>332</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>16</v>
@@ -5277,21 +5340,31 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B87" s="3">
         <v>9.0</v>
       </c>
       <c r="C87" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="D87" s="8"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="8"/>
-      <c r="G87" s="3"/>
-      <c r="H87" s="8"/>
+        <v>7.0</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="H87" s="8" t="s">
+        <v>340</v>
+      </c>
       <c r="I87" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J87" s="5"/>
       <c r="K87" s="5"/>
@@ -5315,13 +5388,13 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B88" s="3">
         <v>9.0</v>
       </c>
       <c r="C88" s="3">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="D88" s="8"/>
       <c r="E88" s="8"/>
@@ -5329,7 +5402,7 @@
       <c r="G88" s="3"/>
       <c r="H88" s="8"/>
       <c r="I88" s="3" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="J88" s="5"/>
       <c r="K88" s="5"/>
@@ -5353,13 +5426,13 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B89" s="3">
         <v>9.0</v>
       </c>
       <c r="C89" s="3">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="D89" s="8"/>
       <c r="E89" s="8"/>
@@ -5391,31 +5464,21 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="B90" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="C90" s="3">
         <v>10.0</v>
       </c>
-      <c r="C90" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D90" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="F90" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="G90" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>331</v>
-      </c>
+      <c r="D90" s="8"/>
+      <c r="E90" s="8"/>
+      <c r="F90" s="8"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="8"/>
       <c r="I90" s="3" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="J90" s="5"/>
       <c r="K90" s="5"/>
@@ -5439,27 +5502,29 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="B91" s="3">
         <v>10.0</v>
       </c>
       <c r="C91" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>333</v>
+        <v>342</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="H91" s="5"/>
+        <v>345</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>346</v>
+      </c>
       <c r="I91" s="3" t="s">
         <v>16</v>
       </c>
@@ -5485,25 +5550,25 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="B92" s="3">
         <v>10.0</v>
       </c>
       <c r="C92" s="3">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>339</v>
+        <v>349</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>350</v>
       </c>
       <c r="H92" s="5"/>
       <c r="I92" s="3" t="s">
@@ -5531,29 +5596,27 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="B93" s="3">
         <v>10.0</v>
       </c>
       <c r="C93" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>342</v>
+        <v>351</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>353</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="H93" s="8" t="s">
-        <v>344</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="H93" s="5"/>
       <c r="I93" s="3" t="s">
         <v>16</v>
       </c>
@@ -5579,31 +5642,31 @@
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="B94" s="3">
         <v>10.0</v>
       </c>
       <c r="C94" s="3">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="F94" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="G94" s="8" t="s">
-        <v>348</v>
+        <v>356</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>358</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J94" s="5"/>
       <c r="K94" s="5"/>
@@ -5627,29 +5690,31 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="B95" s="3">
         <v>10.0</v>
       </c>
       <c r="C95" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>351</v>
+        <v>5.0</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>361</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="H95" s="5"/>
+        <v>363</v>
+      </c>
+      <c r="H95" s="8" t="s">
+        <v>364</v>
+      </c>
       <c r="I95" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J95" s="5"/>
       <c r="K95" s="5"/>
@@ -5673,21 +5738,29 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="B96" s="3">
         <v>10.0</v>
       </c>
       <c r="C96" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="D96" s="5"/>
-      <c r="E96" s="5"/>
-      <c r="F96" s="5"/>
-      <c r="G96" s="5"/>
+        <v>6.0</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>368</v>
+      </c>
       <c r="H96" s="5"/>
       <c r="I96" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J96" s="5"/>
       <c r="K96" s="5"/>
@@ -5711,13 +5784,13 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="B97" s="3">
         <v>10.0</v>
       </c>
       <c r="C97" s="3">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
@@ -5725,7 +5798,7 @@
       <c r="G97" s="5"/>
       <c r="H97" s="5"/>
       <c r="I97" s="3" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="J97" s="5"/>
       <c r="K97" s="5"/>
@@ -5749,13 +5822,13 @@
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="B98" s="3">
         <v>10.0</v>
       </c>
       <c r="C98" s="3">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
@@ -5786,15 +5859,23 @@
       <c r="AB98" s="5"/>
     </row>
     <row r="99">
-      <c r="A99" s="5"/>
-      <c r="B99" s="5"/>
-      <c r="C99" s="5"/>
+      <c r="A99" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B99" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="C99" s="3">
+        <v>9.0</v>
+      </c>
       <c r="D99" s="5"/>
       <c r="E99" s="5"/>
       <c r="F99" s="5"/>
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
-      <c r="I99" s="5"/>
+      <c r="I99" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="J99" s="5"/>
       <c r="K99" s="5"/>
       <c r="L99" s="5"/>
@@ -33535,8 +33616,38 @@
       <c r="AA1023" s="5"/>
       <c r="AB1023" s="5"/>
     </row>
+    <row r="1024">
+      <c r="A1024" s="5"/>
+      <c r="B1024" s="5"/>
+      <c r="C1024" s="5"/>
+      <c r="D1024" s="5"/>
+      <c r="E1024" s="5"/>
+      <c r="F1024" s="5"/>
+      <c r="G1024" s="5"/>
+      <c r="H1024" s="5"/>
+      <c r="I1024" s="5"/>
+      <c r="J1024" s="5"/>
+      <c r="K1024" s="5"/>
+      <c r="L1024" s="5"/>
+      <c r="M1024" s="5"/>
+      <c r="N1024" s="5"/>
+      <c r="O1024" s="5"/>
+      <c r="P1024" s="5"/>
+      <c r="Q1024" s="5"/>
+      <c r="R1024" s="5"/>
+      <c r="S1024" s="5"/>
+      <c r="T1024" s="5"/>
+      <c r="U1024" s="5"/>
+      <c r="V1024" s="5"/>
+      <c r="W1024" s="5"/>
+      <c r="X1024" s="5"/>
+      <c r="Y1024" s="5"/>
+      <c r="Z1024" s="5"/>
+      <c r="AA1024" s="5"/>
+      <c r="AB1024" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:I98">
+  <conditionalFormatting sqref="A2:I99">
     <cfRule type="containsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A2))=0</formula>
     </cfRule>

--- a/experiment/questions.xlsx
+++ b/experiment/questions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tilburgu-my.sharepoint.com/personal/s_m_ostergaard_tilburguniversity_edu/Documents/PhD/self-paced_eeg/natural-stories-dutch/experiment/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ostergaa\OneDrive - Tilburg University\PhD\self-paced_eeg\natural-stories-dutch\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_D0BC670A46EB5C08C0F20DB4C47CD8E240D17436" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38EC4F3D-C890-4E4D-A8B7-D1670F2261F6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDBD1CD-AD28-4201-BC4B-9FBD0045A1A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2857,7 +2857,7 @@
     <t>Jorinde ate a magical berry that transformed her.</t>
   </si>
   <si>
-    <t>Normadisch pastoralisme</t>
+    <t>Nomadisch pastoralisme</t>
   </si>
 </sst>
 </file>
@@ -3151,10 +3151,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>

--- a/experiment/questions.xlsx
+++ b/experiment/questions.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -3338,6 +3338,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>

--- a/experiment/questions.xlsx
+++ b/experiment/questions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tilburgu-my.sharepoint.com/personal/s_m_ostergaard_tilburguniversity_edu/Documents/PhD/self-paced_eeg/natural-stories-dutch/experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_D8882505788B9A89A9744B80D9063E8E1889B84E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41C0683D-9C7C-4BF5-AD98-B187D0E1E916}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_D9882505788B9A89A924CCD34D252E8208CC9F35" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3017,19 +3017,19 @@
     <t>Jorinde en Joringel (practice text)</t>
   </si>
   <si>
-    <t>Waarom was Jorinde in een nachtegaal vernaderd?</t>
-  </si>
-  <si>
-    <t>Jorinde is omgetoverd omdat ze te dicht naar het oude slot toe was gelopen.</t>
-  </si>
-  <si>
-    <t>Joringel heeft Jorinde in een vogel omgetoverd door te zingen.</t>
-  </si>
-  <si>
-    <t>De heks heeft Jorinde achtervolgd om haar in een vogel om te toveren.</t>
-  </si>
-  <si>
-    <t>Jorinde heeft een magische bes gegeten die haar heeft omgetoverd.</t>
+    <t>Wat gebeurt er als een meisje te dicht bij het oude slot komt?</t>
+  </si>
+  <si>
+    <t>Ze kan niet meer bewegen, en de heks verandert haar vervolgens in een vogel.</t>
+  </si>
+  <si>
+    <t>Ze kan niet meer bewegen, en de heks verlost haar vervolgens met een spreuk.</t>
+  </si>
+  <si>
+    <t>Ze verandert meteen in een vogel.</t>
+  </si>
+  <si>
+    <t>Ze kan niet meer bewegen, tot een prins haar komt verlossen.</t>
   </si>
   <si>
     <t>Why was Jorinde turned into a nightingale?</t>
@@ -3338,10 +3338,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -10197,7 +10193,7 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
     </row>
-    <row r="91" spans="1:32" ht="50">
+    <row r="91" spans="1:32" ht="62.5">
       <c r="A91" s="3" t="s">
         <v>933</v>
       </c>
@@ -10229,7 +10225,7 @@
         <v>43</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>45</v>
